--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>源题号</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>B3686</t>
+  </si>
+  <si>
+    <t>B4148</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1103,7 +1106,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1288,6 +1291,14 @@
       </c>
       <c r="B23">
         <v>631</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -1312,7 +1323,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1320,7 +1331,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1328,7 +1339,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1336,7 +1347,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1344,7 +1355,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1352,7 +1363,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1360,7 +1371,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1368,7 +1379,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1396,7 +1407,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1404,7 +1415,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1412,7 +1423,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1420,7 +1431,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>源题号</t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>B4148</t>
+  </si>
+  <si>
+    <t>P1098</t>
+  </si>
+  <si>
+    <t>P7911</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1106,7 +1112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1299,6 +1305,22 @@
       </c>
       <c r="B24">
         <v>639</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +1345,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1331,7 +1353,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1339,7 +1361,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1347,7 +1369,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1355,7 +1377,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1363,7 +1385,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1371,7 +1393,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1379,7 +1401,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1407,7 +1429,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1415,7 +1437,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1423,7 +1445,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1431,7 +1453,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>源题号</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>P7911</t>
+  </si>
+  <si>
+    <t>B4262</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1112,7 +1115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1321,6 +1324,14 @@
       </c>
       <c r="B26">
         <v>641</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1345,7 +1356,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1353,7 +1364,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1361,7 +1372,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1369,7 +1380,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1377,7 +1388,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1385,7 +1396,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1393,7 +1404,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1401,7 +1412,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1429,7 +1440,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1437,7 +1448,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1445,7 +1456,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1453,7 +1464,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
   <si>
     <t>源题号</t>
   </si>
@@ -118,6 +118,15 @@
   </si>
   <si>
     <t>B4262</t>
+  </si>
+  <si>
+    <t>P7910</t>
+  </si>
+  <si>
+    <t>P8651</t>
+  </si>
+  <si>
+    <t>B4579</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1115,7 +1124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1332,6 +1341,30 @@
       </c>
       <c r="B27">
         <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -1356,7 +1389,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1364,7 +1397,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1372,7 +1405,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1380,7 +1413,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1388,7 +1421,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1396,7 +1429,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1404,7 +1437,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1412,7 +1445,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1440,7 +1473,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1448,7 +1481,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1456,7 +1489,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1464,7 +1497,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>源题号</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>B4579</t>
+  </si>
+  <si>
+    <t>P1204</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1124,7 +1127,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1365,6 +1368,14 @@
       </c>
       <c r="B30">
         <v>644</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1400,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1397,7 +1408,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1405,7 +1416,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1413,7 +1424,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1421,7 +1432,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1429,7 +1440,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1437,7 +1448,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1445,7 +1456,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1473,7 +1484,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1481,7 +1492,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1489,7 +1500,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1497,7 +1508,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>源题号</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>P1204</t>
+  </si>
+  <si>
+    <t>P5250</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1127,7 +1130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1376,6 +1379,14 @@
       </c>
       <c r="B31">
         <v>645</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -1400,7 +1411,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1408,7 +1419,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1416,7 +1427,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1424,7 +1435,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1432,7 +1443,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1440,7 +1451,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1448,7 +1459,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1456,7 +1467,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1484,7 +1495,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1492,7 +1503,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1500,7 +1511,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1508,7 +1519,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>源题号</t>
   </si>
@@ -135,6 +135,12 @@
     <t>P5250</t>
   </si>
   <si>
+    <t>B3778</t>
+  </si>
+  <si>
+    <t>B3915</t>
+  </si>
+  <si>
     <t>cf1668b</t>
   </si>
   <si>
@@ -157,6 +163,9 @@
   </si>
   <si>
     <t>cf255a</t>
+  </si>
+  <si>
+    <t>cf2266a</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1130,8 +1139,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1387,6 +1396,22 @@
       </c>
       <c r="B32">
         <v>650</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -1398,8 +1423,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1411,7 +1436,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1419,7 +1444,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1427,7 +1452,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1435,7 +1460,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1443,7 +1468,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1451,7 +1476,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1459,7 +1484,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1467,10 +1492,18 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>630</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10">
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -1483,7 +1516,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1495,7 +1528,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1503,7 +1536,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1511,7 +1544,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1519,7 +1552,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>源题号</t>
   </si>
@@ -141,6 +141,15 @@
     <t>B3915</t>
   </si>
   <si>
+    <t>P2367</t>
+  </si>
+  <si>
+    <t>P9749</t>
+  </si>
+  <si>
+    <t>P5661</t>
+  </si>
+  <si>
     <t>cf1668b</t>
   </si>
   <si>
@@ -166,6 +175,12 @@
   </si>
   <si>
     <t>cf2266a</t>
+  </si>
+  <si>
+    <t>cf1517a</t>
+  </si>
+  <si>
+    <t>cf1285a</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1139,7 +1154,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1412,6 +1427,30 @@
       </c>
       <c r="B34">
         <v>655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1462,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1436,7 +1475,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1444,7 +1483,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1452,7 +1491,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1460,7 +1499,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1468,7 +1507,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1476,7 +1515,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1484,7 +1523,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1492,7 +1531,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1500,10 +1539,26 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>653</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12">
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -1528,7 +1583,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1536,7 +1591,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1544,7 +1599,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1552,7 +1607,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>源题号</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>P5661</t>
+  </si>
+  <si>
+    <t>B3888</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1154,7 +1157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1451,6 +1454,14 @@
       </c>
       <c r="B37">
         <v>659</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>662</v>
       </c>
     </row>
   </sheetData>
@@ -1475,7 +1486,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1483,7 +1494,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1491,7 +1502,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1499,7 +1510,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1507,7 +1518,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1515,7 +1526,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1523,7 +1534,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1531,7 +1542,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1539,7 +1550,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10">
         <v>653</v>
@@ -1547,7 +1558,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11">
         <v>660</v>
@@ -1555,7 +1566,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>661</v>
@@ -1583,7 +1594,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1591,7 +1602,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1599,7 +1610,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1607,7 +1618,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>源题号</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>cf1285a</t>
+  </si>
+  <si>
+    <t>cf59b</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1158,7 +1161,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1473,8 +1476,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1570,6 +1573,14 @@
       </c>
       <c r="B12">
         <v>661</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13">
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -1582,7 +1593,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1594,7 +1605,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1602,7 +1613,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1610,7 +1621,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1618,7 +1629,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5">
         <v>600</v>
